--- a/catalogs/TABLE_CATALOG.xlsx
+++ b/catalogs/TABLE_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TABLE_CATALOG" sheetId="1" r:id="Rcae094e4ba824691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TABLE_CATALOG" sheetId="1" r:id="R6c12182b44aa4c1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,6 +52,11 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2436"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -60,7 +65,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +104,10 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -314,28 +323,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="45" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="17" t="str">
         <x:v>table</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="17" t="str">
         <x:v>chapter</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="17" t="str">
         <x:v>chapter_title</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="17" t="str">
         <x:v>caption</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="17" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="17" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="17" t="str">
         <x:v>release_date</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="17" t="str">
         <x:v>source_book_page</x:v>
       </x:c>
     </x:row>
